--- a/LexIA_Diario/config/metricas_julio_2026_indicadores.xlsx
+++ b/LexIA_Diario/config/metricas_julio_2026_indicadores.xlsx
@@ -8,8 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/LexIA_Diario/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_805357ABFC1C6E9BD651B69DE1322B816A7FB77E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176D1083-4B01-45AC-AF9E-419867A423E9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resumen" sheetId="1" r:id="rId1"/>
@@ -26,7 +27,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">norma_por_norma!$A$1:$J$94</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1077,12 +1091,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1097,8 +1117,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1402,12 +1423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="1" max="1" width="41.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1415,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1423,7 +1445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1431,7 +1453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1439,7 +1461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1447,7 +1469,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1455,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1463,7 +1485,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1471,7 +1493,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1479,7 +1501,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1487,7 +1509,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1495,7 +1517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1503,15 +1525,15 @@
         <v>0.32098765432098758</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1519,7 +1541,7 @@
         <v>0.43697478991596639</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1527,7 +1549,7 @@
         <v>0.3708898944193062</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1535,7 +1557,7 @@
         <v>0.60277777777777775</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1551,9 +1573,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1561,7 +1583,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1569,7 +1591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1577,7 +1599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1585,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -1593,7 +1615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -1601,7 +1623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -1609,7 +1631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -1625,7 +1647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -1633,7 +1655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -1649,12 +1671,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1662,7 +1684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1670,7 +1692,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1678,7 +1700,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1686,7 +1708,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1694,7 +1716,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1702,7 +1724,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1710,7 +1732,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1718,7 +1740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1726,7 +1748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1734,7 +1756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1750,9 +1772,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1790,7 +1815,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1828,7 +1853,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -1866,7 +1891,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1904,7 +1929,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -1942,7 +1967,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -1980,7 +2005,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -2015,7 +2040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -2044,7 +2069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -2082,7 +2107,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -2120,7 +2145,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -2149,7 +2174,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -2178,7 +2203,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -2207,7 +2232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -2236,7 +2261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -2274,7 +2299,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2312,7 +2337,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -2347,7 +2372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -2382,7 +2407,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2411,7 +2436,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -2440,7 +2465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2478,7 +2503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -2507,7 +2532,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -2542,7 +2567,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2580,7 +2605,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>67</v>
       </c>
@@ -2615,7 +2640,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -2653,7 +2678,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -2682,7 +2707,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -2711,7 +2736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -2740,7 +2765,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -2772,7 +2797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2808,11 +2833,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2844,7 +2868,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2864,7 +2888,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2887,7 +2911,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2919,7 +2943,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2951,7 +2975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2983,7 +3007,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3015,7 +3039,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3035,7 +3059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -3058,7 +3082,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -3081,7 +3105,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -3113,7 +3137,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -3145,7 +3169,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -3177,7 +3201,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -3209,7 +3233,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -3232,7 +3256,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -3255,7 +3279,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -3287,7 +3311,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -3319,7 +3343,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -3351,7 +3375,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -3374,7 +3398,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -3397,7 +3421,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -3429,7 +3453,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -3452,7 +3476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -3475,7 +3499,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -3507,7 +3531,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -3527,7 +3551,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -3550,7 +3574,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -3573,7 +3597,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -3596,7 +3620,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>53</v>
       </c>
@@ -3619,7 +3643,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -3642,7 +3666,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -3665,7 +3689,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -3697,7 +3721,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -3720,7 +3744,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -3743,7 +3767,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -3766,7 +3790,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -3789,7 +3813,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -3821,7 +3845,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -3841,7 +3865,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>59</v>
       </c>
@@ -3873,7 +3897,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>59</v>
       </c>
@@ -3905,7 +3929,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -3937,7 +3961,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -3960,7 +3984,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -3983,7 +4007,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -4006,7 +4030,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -4029,7 +4053,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -4052,7 +4076,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -4075,7 +4099,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -4098,7 +4122,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>28</v>
       </c>
@@ -4121,7 +4145,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>28</v>
       </c>
@@ -4144,7 +4168,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -4167,7 +4191,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>28</v>
       </c>
@@ -4190,7 +4214,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>28</v>
       </c>
@@ -4213,7 +4237,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>28</v>
       </c>
@@ -4236,7 +4260,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -4259,7 +4283,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -4282,7 +4306,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -4305,7 +4329,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>28</v>
       </c>
@@ -4328,7 +4352,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>28</v>
       </c>
@@ -4351,7 +4375,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -4374,7 +4398,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -4397,7 +4421,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -4420,7 +4444,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -4443,7 +4467,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -4466,7 +4490,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -4489,7 +4513,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -4512,7 +4536,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>28</v>
       </c>
@@ -4544,7 +4568,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -4564,7 +4588,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -4584,7 +4608,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -4607,7 +4631,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>30</v>
       </c>
@@ -4630,7 +4654,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>60</v>
       </c>
@@ -4650,7 +4674,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>60</v>
       </c>
@@ -4673,7 +4697,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>60</v>
       </c>
@@ -4696,7 +4720,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>63</v>
       </c>
@@ -4716,7 +4740,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>63</v>
       </c>
@@ -4739,7 +4763,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>63</v>
       </c>
@@ -4771,7 +4795,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -4791,7 +4815,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>65</v>
       </c>
@@ -4814,7 +4838,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>65</v>
       </c>
@@ -4837,7 +4861,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>65</v>
       </c>
@@ -4860,7 +4884,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -4883,7 +4907,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -4906,7 +4930,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -4938,7 +4962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -4970,7 +4994,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -5002,7 +5026,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -5034,7 +5058,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>67</v>
       </c>
@@ -5054,7 +5078,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>67</v>
       </c>
@@ -5074,7 +5098,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -5097,7 +5121,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>68</v>
       </c>
@@ -5129,7 +5153,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>68</v>
       </c>
@@ -5161,7 +5185,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>72</v>
       </c>
@@ -5182,13 +5206,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="FN"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J94" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5196,9 +5214,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>73</v>
       </c>
@@ -5206,7 +5224,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -5214,7 +5232,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -5222,7 +5240,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -5238,9 +5256,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -5263,7 +5284,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -5286,7 +5307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>59</v>
       </c>
@@ -5309,7 +5330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5332,7 +5353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -5355,7 +5376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -5386,9 +5407,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -5411,7 +5432,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -5434,7 +5455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -5457,7 +5478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -5480,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -5500,7 +5521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -5528,9 +5549,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -5553,7 +5574,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -5573,7 +5594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -5593,7 +5614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -5613,7 +5634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -5636,7 +5657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -5664,9 +5685,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -5674,7 +5695,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -5682,7 +5703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -5690,7 +5711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -5698,7 +5719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -5706,7 +5727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -5714,7 +5735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -5722,7 +5743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -5730,7 +5751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -5738,7 +5759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -5746,7 +5767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -5754,7 +5775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5762,7 +5783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5770,7 +5791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -5778,7 +5799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -5786,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
